--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251025.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251025.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,6 +732,303 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2458GCC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cake Circle - 8" (Gold)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>39.49</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>78.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>24510GCC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cake Circle - 10" (Gold)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>54.99</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>109.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>245882WB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Box Cake - 8x8x2.5 (window)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>68.60</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>137.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>588MILK632</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Urnex - Rinza</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>17.99</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>35.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>150BB4224N</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bag Paper - Baguette</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>118.99</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>237.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>433qlinerbl</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - White</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>46.99</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>140.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>53A213012</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Simple Green - Degreaser</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>73.44</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>146.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>707U72SPRDBK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Black Plastic Spreader 7.51"</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>18.49</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>36.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>500L4B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lid Espresso - 4oz</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>61.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5004CAFE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cup - Espresso (4oz)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>35.49</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>70.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>182RRF8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bag - Poly (Retail Portion)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>21.97</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>43.94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
